--- a/GMAX2518/РАСПИНОВКА_0505_2518.xlsx
+++ b/GMAX2518/РАСПИНОВКА_0505_2518.xlsx
@@ -260,11 +260,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,33 +549,35 @@
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.28515625" style="1" customWidth="1"/>
-    <col min="5" max="7" width="9.140625" style="1"/>
+    <col min="5" max="5" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="5"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -584,7 +586,7 @@
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D2" s="3"/>
@@ -594,7 +596,7 @@
       <c r="F2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>39</v>
       </c>
       <c r="H2" s="3"/>
@@ -612,7 +614,7 @@
       <c r="B3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -620,7 +622,7 @@
       <c r="F3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="5"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1">
         <v>1</v>
@@ -636,7 +638,7 @@
       <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1" t="s">
         <v>4</v>
@@ -644,7 +646,7 @@
       <c r="F4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="5"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1">
         <v>2</v>
@@ -660,7 +662,7 @@
       <c r="B5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="3"/>
       <c r="E5" s="1" t="s">
         <v>5</v>
@@ -668,7 +670,7 @@
       <c r="F5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="5"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -678,7 +680,7 @@
       <c r="B6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="3"/>
       <c r="E6" s="1" t="s">
         <v>6</v>
@@ -686,12 +688,12 @@
       <c r="F6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="5"/>
+      <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -700,7 +702,7 @@
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="3"/>
       <c r="E7" s="1" t="s">
         <v>7</v>
@@ -708,7 +710,7 @@
       <c r="F7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="4"/>
+      <c r="G7" s="5"/>
       <c r="H7" s="3"/>
       <c r="I7" s="1">
         <v>0</v>
@@ -724,7 +726,7 @@
       <c r="B8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="3"/>
       <c r="E8" s="1" t="s">
         <v>8</v>
@@ -732,7 +734,7 @@
       <c r="F8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="5"/>
       <c r="H8" s="3"/>
       <c r="I8" s="1">
         <v>1</v>
@@ -748,7 +750,7 @@
       <c r="B9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="3"/>
       <c r="E9" s="1" t="s">
         <v>9</v>
@@ -756,7 +758,7 @@
       <c r="F9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="5"/>
       <c r="H9" s="3"/>
       <c r="I9" s="1">
         <v>2</v>
@@ -776,7 +778,7 @@
       <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D11" s="3"/>
@@ -786,14 +788,14 @@
       <c r="F11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="5"/>
+      <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -802,7 +804,7 @@
       <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="3"/>
       <c r="E12" s="1" t="s">
         <v>11</v>
@@ -810,7 +812,7 @@
       <c r="F12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="4"/>
+      <c r="G12" s="5"/>
       <c r="H12" s="3"/>
       <c r="I12" s="1">
         <v>0</v>
@@ -826,7 +828,7 @@
       <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="3"/>
       <c r="E13" s="1" t="s">
         <v>12</v>
@@ -834,7 +836,7 @@
       <c r="F13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="5"/>
       <c r="H13" s="3"/>
       <c r="I13" s="1">
         <v>1</v>
@@ -850,7 +852,7 @@
       <c r="B14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="3"/>
       <c r="E14" s="1" t="s">
         <v>13</v>
@@ -858,7 +860,7 @@
       <c r="F14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="4"/>
+      <c r="G14" s="5"/>
       <c r="H14" s="3"/>
       <c r="I14" s="1">
         <v>2</v>
@@ -874,7 +876,7 @@
       <c r="B15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="3"/>
       <c r="E15" s="1" t="s">
         <v>14</v>
@@ -882,7 +884,7 @@
       <c r="F15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="4"/>
+      <c r="G15" s="5"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -892,7 +894,7 @@
       <c r="B16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="3"/>
       <c r="E16" s="1" t="s">
         <v>15</v>
@@ -900,12 +902,12 @@
       <c r="F16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="4"/>
+      <c r="G16" s="5"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="5"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -914,7 +916,7 @@
       <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="4"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="3"/>
       <c r="E17" s="1" t="s">
         <v>16</v>
@@ -922,7 +924,7 @@
       <c r="F17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="4"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="3"/>
       <c r="I17" s="1">
         <v>0</v>
@@ -938,7 +940,7 @@
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="3"/>
       <c r="E18" s="1" t="s">
         <v>17</v>
@@ -946,7 +948,7 @@
       <c r="F18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="4"/>
+      <c r="G18" s="5"/>
       <c r="H18" s="3"/>
       <c r="I18" s="1">
         <v>1</v>
@@ -970,7 +972,7 @@
       <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="3"/>
@@ -980,7 +982,7 @@
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>35</v>
       </c>
       <c r="H20" s="3"/>
@@ -992,7 +994,7 @@
       <c r="B21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="D21" s="3"/>
       <c r="E21" s="1" t="s">
         <v>19</v>
@@ -1000,7 +1002,7 @@
       <c r="F21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="4"/>
+      <c r="G21" s="5"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1010,7 +1012,7 @@
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="3"/>
       <c r="E22" s="1" t="s">
         <v>20</v>
@@ -1018,7 +1020,7 @@
       <c r="F22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="4"/>
+      <c r="G22" s="5"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1028,7 +1030,7 @@
       <c r="B23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="3"/>
       <c r="E23" s="1" t="s">
         <v>21</v>
@@ -1036,7 +1038,7 @@
       <c r="F23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G23" s="4"/>
+      <c r="G23" s="5"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1046,7 +1048,7 @@
       <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="4"/>
+      <c r="C24" s="5"/>
       <c r="D24" s="3"/>
       <c r="E24" s="1" t="s">
         <v>22</v>
@@ -1054,7 +1056,7 @@
       <c r="F24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="4"/>
+      <c r="G24" s="5"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1064,7 +1066,7 @@
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="3"/>
       <c r="E25" s="1" t="s">
         <v>23</v>
@@ -1072,7 +1074,7 @@
       <c r="F25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="4"/>
+      <c r="G25" s="5"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1082,7 +1084,7 @@
       <c r="B26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C26" s="5"/>
       <c r="D26" s="3"/>
       <c r="E26" s="1" t="s">
         <v>24</v>
@@ -1090,7 +1092,7 @@
       <c r="F26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="4"/>
+      <c r="G26" s="5"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1100,7 +1102,7 @@
       <c r="B27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="3"/>
       <c r="E27" s="1" t="s">
         <v>25</v>
@@ -1108,7 +1110,7 @@
       <c r="F27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="4"/>
+      <c r="G27" s="5"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1122,7 +1124,7 @@
       <c r="B29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D29" s="3"/>
@@ -1132,7 +1134,7 @@
       <c r="F29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>39</v>
       </c>
       <c r="H29" s="3"/>
@@ -1144,7 +1146,7 @@
       <c r="B30" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="4"/>
+      <c r="C30" s="5"/>
       <c r="D30" s="3"/>
       <c r="E30" s="1" t="s">
         <v>27</v>
@@ -1152,7 +1154,7 @@
       <c r="F30" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G30" s="4"/>
+      <c r="G30" s="5"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1162,7 +1164,7 @@
       <c r="B31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="4"/>
+      <c r="C31" s="5"/>
       <c r="D31" s="3"/>
       <c r="E31" s="1" t="s">
         <v>28</v>
@@ -1170,25 +1172,25 @@
       <c r="F31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="4"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="G20:G27"/>
+    <mergeCell ref="G11:G18"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C20:C27"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="C2:C9"/>
     <mergeCell ref="C11:C18"/>
     <mergeCell ref="G2:G9"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="G20:G27"/>
-    <mergeCell ref="G11:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
